--- a/Picker tracker.xlsx
+++ b/Picker tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snowfoxgroup.sharepoint.com/sites/DISPACHcopy/Shared Documents/General/08. Holiday and Labour Planning/Daily Staffing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="10_ncr:8000_{B1278633-C007-43BB-84BD-AFBFF3590D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45B1C12A-FE23-418E-8F2C-993A68947411}"/>
+  <xr:revisionPtr revIDLastSave="886" documentId="10_ncr:8000_{B1278633-C007-43BB-84BD-AFBFF3590D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73462F55-A461-4E0D-9DF7-DD279E97263C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4544" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4994" uniqueCount="423">
   <si>
     <t>Yogesh Chaudhari</t>
   </si>
@@ -1223,6 +1223,93 @@
   <si>
     <t>Neel</t>
   </si>
+  <si>
+    <t xml:space="preserve">Mangesh Amrutlal </t>
+  </si>
+  <si>
+    <t>ag shridhar</t>
+  </si>
+  <si>
+    <t>Viraj Chavada</t>
+  </si>
+  <si>
+    <t>lulien</t>
+  </si>
+  <si>
+    <t>andre</t>
+  </si>
+  <si>
+    <t>ag chirag</t>
+  </si>
+  <si>
+    <t>ag hansmukh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardik Savaliya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmin Kanti </t>
+  </si>
+  <si>
+    <t>ag kaber</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ag Bhavasinn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ag bharati </t>
+  </si>
+  <si>
+    <t>ag pinkal</t>
+  </si>
+  <si>
+    <t>ag biren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ag kabber </t>
+  </si>
+  <si>
+    <t>AG (Hanshmukh)</t>
+  </si>
+  <si>
+    <t>AG (moin)</t>
+  </si>
+  <si>
+    <t>Mangesh Amrutla</t>
+  </si>
+  <si>
+    <t>Vishrut</t>
+  </si>
+  <si>
+    <t>ag dhruvil</t>
+  </si>
+  <si>
+    <t>ag bharat</t>
+  </si>
+  <si>
+    <t>ag raj</t>
+  </si>
+  <si>
+    <t>ag nisarg mukeshbhai</t>
+  </si>
+  <si>
+    <t>Mangesh Amrutlal (TL)</t>
+  </si>
+  <si>
+    <t>rahul patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viraj </t>
+  </si>
+  <si>
+    <t>hardik patel</t>
+  </si>
+  <si>
+    <t>Jasmin Kanti (AS)</t>
+  </si>
+  <si>
+    <t>edwin</t>
+  </si>
 </sst>
 </file>
 
@@ -1347,7 +1434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1383,6 +1470,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1408,8 +1496,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1EEF5E04-9FF3-4FE3-BFF5-CC0DCC0EA915}" name="Table2" displayName="Table2" ref="A1:E4415" totalsRowShown="0">
-  <autoFilter ref="A1:E4415" xr:uid="{1EEF5E04-9FF3-4FE3-BFF5-CC0DCC0EA915}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1EEF5E04-9FF3-4FE3-BFF5-CC0DCC0EA915}" name="Table2" displayName="Table2" ref="A1:E4865" totalsRowShown="0">
+  <autoFilter ref="A1:E4865" xr:uid="{1EEF5E04-9FF3-4FE3-BFF5-CC0DCC0EA915}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4415">
     <sortCondition ref="A1:A4415"/>
   </sortState>
@@ -2242,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB6B554-0230-40F4-9302-9A4A55BFD273}">
-  <dimension ref="A1:E4415"/>
+  <dimension ref="A1:E4865"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
@@ -81763,6 +81851,8106 @@
         <v>NIGHT</v>
       </c>
     </row>
+    <row r="4416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4416" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4416" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4416">
+        <v>10737</v>
+      </c>
+      <c r="D4416">
+        <v>14500</v>
+      </c>
+      <c r="E4416" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4417" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4417" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4417">
+        <v>9877</v>
+      </c>
+      <c r="D4417">
+        <v>13600</v>
+      </c>
+      <c r="E4417" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4418" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4418" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4418">
+        <v>9741</v>
+      </c>
+      <c r="D4418">
+        <v>15000</v>
+      </c>
+      <c r="E4418" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4419" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4419" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4419">
+        <v>8908</v>
+      </c>
+      <c r="D4419">
+        <v>9000</v>
+      </c>
+      <c r="E4419" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4420" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4420" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4420">
+        <v>8484</v>
+      </c>
+      <c r="D4420">
+        <v>8500</v>
+      </c>
+      <c r="E4420" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4421" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4421" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4421">
+        <v>8288</v>
+      </c>
+      <c r="D4421">
+        <v>8500</v>
+      </c>
+      <c r="E4421" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4422" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4422" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4422">
+        <v>7644</v>
+      </c>
+      <c r="D4422">
+        <v>7750</v>
+      </c>
+      <c r="E4422" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4423" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4423" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4423">
+        <v>7094</v>
+      </c>
+      <c r="D4423">
+        <v>12000</v>
+      </c>
+      <c r="E4423" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4424" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4424" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4424">
+        <v>6580</v>
+      </c>
+      <c r="D4424">
+        <v>4500</v>
+      </c>
+      <c r="E4424" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4425" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4425" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4425">
+        <v>6248</v>
+      </c>
+      <c r="D4425">
+        <v>6500</v>
+      </c>
+      <c r="E4425" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4426" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4426" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4426">
+        <v>6224</v>
+      </c>
+      <c r="D4426">
+        <v>4000</v>
+      </c>
+      <c r="E4426" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4427" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4427" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4427">
+        <v>6074</v>
+      </c>
+      <c r="D4427">
+        <v>4000</v>
+      </c>
+      <c r="E4427" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4428" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4428" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4428">
+        <v>5780</v>
+      </c>
+      <c r="D4428">
+        <v>4000</v>
+      </c>
+      <c r="E4428" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4429" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4429" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4429">
+        <v>4112</v>
+      </c>
+      <c r="D4429">
+        <v>4000</v>
+      </c>
+      <c r="E4429" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4430" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4430" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4430">
+        <v>4112</v>
+      </c>
+      <c r="D4430">
+        <v>4000</v>
+      </c>
+      <c r="E4430" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4431" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4431" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4431">
+        <v>4098</v>
+      </c>
+      <c r="D4431">
+        <v>8000</v>
+      </c>
+      <c r="E4431" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4432" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4432" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4432">
+        <v>3960</v>
+      </c>
+      <c r="D4432">
+        <v>8000</v>
+      </c>
+      <c r="E4432" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4433" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4433" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4433">
+        <v>3922</v>
+      </c>
+      <c r="D4433">
+        <v>8000</v>
+      </c>
+      <c r="E4433" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4434" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4434" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4434">
+        <v>3800</v>
+      </c>
+      <c r="D4434">
+        <v>4000</v>
+      </c>
+      <c r="E4434" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4435" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4435" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4435">
+        <v>3800</v>
+      </c>
+      <c r="D4435">
+        <v>4000</v>
+      </c>
+      <c r="E4435" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4436" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4436" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4436">
+        <v>3797</v>
+      </c>
+      <c r="D4436">
+        <v>8000</v>
+      </c>
+      <c r="E4436" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4437" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4437" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4437">
+        <v>3787</v>
+      </c>
+      <c r="D4437">
+        <v>8000</v>
+      </c>
+      <c r="E4437" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4438" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4438" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4438">
+        <v>3766</v>
+      </c>
+      <c r="D4438">
+        <v>8000</v>
+      </c>
+      <c r="E4438" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4439" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4439" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4439">
+        <v>3646</v>
+      </c>
+      <c r="D4439">
+        <v>8000</v>
+      </c>
+      <c r="E4439" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4440" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4440" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4440">
+        <v>3620</v>
+      </c>
+      <c r="D4440">
+        <v>4000</v>
+      </c>
+      <c r="E4440" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4441" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4441" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4441">
+        <v>3581</v>
+      </c>
+      <c r="D4441">
+        <v>2750</v>
+      </c>
+      <c r="E4441" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4442" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4442" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4442">
+        <v>3581</v>
+      </c>
+      <c r="D4442">
+        <v>2750</v>
+      </c>
+      <c r="E4442" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4443" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4443" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4443">
+        <v>3470</v>
+      </c>
+      <c r="D4443">
+        <v>8000</v>
+      </c>
+      <c r="E4443" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4444" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4444" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4444">
+        <v>3365</v>
+      </c>
+      <c r="D4444">
+        <v>4000</v>
+      </c>
+      <c r="E4444" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4445" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4445" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4445">
+        <v>3332</v>
+      </c>
+      <c r="D4445">
+        <v>36000</v>
+      </c>
+      <c r="E4445" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4446" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4446" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4446">
+        <v>3292</v>
+      </c>
+      <c r="D4446">
+        <v>4000</v>
+      </c>
+      <c r="E4446" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4447" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4447" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4447">
+        <v>3085</v>
+      </c>
+      <c r="D4447">
+        <v>8000</v>
+      </c>
+      <c r="E4447" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4448" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4448" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4448">
+        <v>2599</v>
+      </c>
+      <c r="D4448">
+        <v>2250</v>
+      </c>
+      <c r="E4448" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4449" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4449" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4449">
+        <v>2599</v>
+      </c>
+      <c r="D4449">
+        <v>2250</v>
+      </c>
+      <c r="E4449" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4450" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4450" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4450">
+        <v>2340</v>
+      </c>
+      <c r="D4450">
+        <v>2500</v>
+      </c>
+      <c r="E4450" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4451" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4451" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4451">
+        <v>1978</v>
+      </c>
+      <c r="D4451">
+        <v>2000</v>
+      </c>
+      <c r="E4451" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4452" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4452" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4452">
+        <v>1887</v>
+      </c>
+      <c r="D4452">
+        <v>2000</v>
+      </c>
+      <c r="E4452" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4453" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4453" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4453">
+        <v>1818</v>
+      </c>
+      <c r="D4453">
+        <v>2000</v>
+      </c>
+      <c r="E4453" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4454" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4454" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4454" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4454">
+        <v>1744</v>
+      </c>
+      <c r="D4454">
+        <v>6400</v>
+      </c>
+      <c r="E4454" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4455" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4455" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4455" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4455">
+        <v>1090</v>
+      </c>
+      <c r="D4455">
+        <v>1000</v>
+      </c>
+      <c r="E4455" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4456" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4456" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4456">
+        <v>622</v>
+      </c>
+      <c r="D4456">
+        <v>4000</v>
+      </c>
+      <c r="E4456" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4457" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4457" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4457">
+        <v>466</v>
+      </c>
+      <c r="D4457">
+        <v>2400</v>
+      </c>
+      <c r="E4457" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4458" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4458" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4458">
+        <v>400</v>
+      </c>
+      <c r="D4458">
+        <v>500</v>
+      </c>
+      <c r="E4458" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4459" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4459" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4459">
+        <v>360</v>
+      </c>
+      <c r="D4459">
+        <v>375</v>
+      </c>
+      <c r="E4459" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4460" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4460" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4460">
+        <v>218</v>
+      </c>
+      <c r="D4460">
+        <v>7200</v>
+      </c>
+      <c r="E4460" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4461" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B4461" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4461">
+        <v>120</v>
+      </c>
+      <c r="D4461">
+        <v>4000</v>
+      </c>
+      <c r="E4461" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4462" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4462" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4462">
+        <v>6659</v>
+      </c>
+      <c r="D4462">
+        <v>4750</v>
+      </c>
+      <c r="E4462" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4463" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4463" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4463">
+        <v>6609</v>
+      </c>
+      <c r="D4463">
+        <v>4250</v>
+      </c>
+      <c r="E4463" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4464" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4464" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4464">
+        <v>6509</v>
+      </c>
+      <c r="D4464">
+        <v>6500</v>
+      </c>
+      <c r="E4464" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4465" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4465" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4465">
+        <v>6339</v>
+      </c>
+      <c r="D4465">
+        <v>4000</v>
+      </c>
+      <c r="E4465" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4466" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4466" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4466">
+        <v>6339</v>
+      </c>
+      <c r="D4466">
+        <v>4000</v>
+      </c>
+      <c r="E4466" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4467" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4467" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4467">
+        <v>5023</v>
+      </c>
+      <c r="D4467">
+        <v>8500</v>
+      </c>
+      <c r="E4467" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4468" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4468" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4468">
+        <v>4923</v>
+      </c>
+      <c r="D4468">
+        <v>8500</v>
+      </c>
+      <c r="E4468" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4469" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4469" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4469">
+        <v>4190</v>
+      </c>
+      <c r="D4469">
+        <v>4250</v>
+      </c>
+      <c r="E4469" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4470" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4470" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4470">
+        <v>4090</v>
+      </c>
+      <c r="D4470">
+        <v>4250</v>
+      </c>
+      <c r="E4470" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4471" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4471" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4471">
+        <v>4008</v>
+      </c>
+      <c r="D4471">
+        <v>29750</v>
+      </c>
+      <c r="E4471" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4472" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4472" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4472">
+        <v>3921</v>
+      </c>
+      <c r="D4472">
+        <v>4000</v>
+      </c>
+      <c r="E4472" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4473" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4473" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4473">
+        <v>3890</v>
+      </c>
+      <c r="D4473">
+        <v>4250</v>
+      </c>
+      <c r="E4473" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4474" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4474" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4474">
+        <v>3890</v>
+      </c>
+      <c r="D4474">
+        <v>4250</v>
+      </c>
+      <c r="E4474" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4475" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4475" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4475">
+        <v>3790</v>
+      </c>
+      <c r="D4475">
+        <v>4250</v>
+      </c>
+      <c r="E4475" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4476" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4476" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4476">
+        <v>3678</v>
+      </c>
+      <c r="D4476">
+        <v>4250</v>
+      </c>
+      <c r="E4476" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4477" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4477" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4477" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4477">
+        <v>3590</v>
+      </c>
+      <c r="D4477">
+        <v>4250</v>
+      </c>
+      <c r="E4477" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4478" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4478" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4478">
+        <v>3553</v>
+      </c>
+      <c r="D4478">
+        <v>4000</v>
+      </c>
+      <c r="E4478" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4479" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4479" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4479" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4479">
+        <v>3502</v>
+      </c>
+      <c r="D4479">
+        <v>3500</v>
+      </c>
+      <c r="E4479" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4480" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4480" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4480">
+        <v>3469</v>
+      </c>
+      <c r="D4480">
+        <v>4000</v>
+      </c>
+      <c r="E4480" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4481" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4481" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4481" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4481">
+        <v>2780</v>
+      </c>
+      <c r="D4481">
+        <v>4250</v>
+      </c>
+      <c r="E4481" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4482" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4482" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4482" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4482">
+        <v>2769</v>
+      </c>
+      <c r="D4482">
+        <v>3000</v>
+      </c>
+      <c r="E4482" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4483" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4483" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4483" t="s">
+        <v>404</v>
+      </c>
+      <c r="C4483">
+        <v>2690</v>
+      </c>
+      <c r="D4483">
+        <v>4250</v>
+      </c>
+      <c r="E4483" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4484" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4484" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4484" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4484">
+        <v>2630</v>
+      </c>
+      <c r="D4484">
+        <v>2500</v>
+      </c>
+      <c r="E4484" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4485" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4485" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4485" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4485">
+        <v>2590</v>
+      </c>
+      <c r="D4485">
+        <v>4250</v>
+      </c>
+      <c r="E4485" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4486" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4486" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4486">
+        <v>2178</v>
+      </c>
+      <c r="D4486">
+        <v>4250</v>
+      </c>
+      <c r="E4486" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4487" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4487" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4487" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4487">
+        <v>2160</v>
+      </c>
+      <c r="D4487">
+        <v>2500</v>
+      </c>
+      <c r="E4487" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4488" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4488" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4488">
+        <v>2156</v>
+      </c>
+      <c r="D4488">
+        <v>2000</v>
+      </c>
+      <c r="E4488" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4489" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4489" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4489">
+        <v>1256</v>
+      </c>
+      <c r="D4489">
+        <v>1250</v>
+      </c>
+      <c r="E4489" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4490" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4490" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4490">
+        <v>1060</v>
+      </c>
+      <c r="D4490">
+        <v>1000</v>
+      </c>
+      <c r="E4490" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4491" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4491" t="s">
+        <v>406</v>
+      </c>
+      <c r="C4491">
+        <v>780</v>
+      </c>
+      <c r="D4491">
+        <v>4250</v>
+      </c>
+      <c r="E4491" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4492" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B4492" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4492">
+        <v>187</v>
+      </c>
+      <c r="D4492">
+        <v>7650</v>
+      </c>
+      <c r="E4492" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4493" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4493" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4493">
+        <v>13897</v>
+      </c>
+      <c r="D4493">
+        <v>15000</v>
+      </c>
+      <c r="E4493" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4494" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4494" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4494">
+        <v>10105</v>
+      </c>
+      <c r="D4494">
+        <v>11500</v>
+      </c>
+      <c r="E4494" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4495" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4495" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4495">
+        <v>9521</v>
+      </c>
+      <c r="D4495">
+        <v>11000</v>
+      </c>
+      <c r="E4495" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4496" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4496" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4496">
+        <v>6208</v>
+      </c>
+      <c r="D4496">
+        <v>6500</v>
+      </c>
+      <c r="E4496" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4497" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4497" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4497">
+        <v>5775</v>
+      </c>
+      <c r="D4497">
+        <v>4000</v>
+      </c>
+      <c r="E4497" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4498" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4498" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4498" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4498">
+        <v>5775</v>
+      </c>
+      <c r="D4498">
+        <v>4000</v>
+      </c>
+      <c r="E4498" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4499" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4499" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4499">
+        <v>4527</v>
+      </c>
+      <c r="D4499">
+        <v>3000</v>
+      </c>
+      <c r="E4499" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4500" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4500" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4500" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4500">
+        <v>4527</v>
+      </c>
+      <c r="D4500">
+        <v>3000</v>
+      </c>
+      <c r="E4500" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4501" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4501" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4501" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4501">
+        <v>4296</v>
+      </c>
+      <c r="D4501">
+        <v>10500</v>
+      </c>
+      <c r="E4501" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4502" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4502" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4502" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4502">
+        <v>4270</v>
+      </c>
+      <c r="D4502">
+        <v>8000</v>
+      </c>
+      <c r="E4502" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4503" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4503" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4503" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4503">
+        <v>4232</v>
+      </c>
+      <c r="D4503">
+        <v>4500</v>
+      </c>
+      <c r="E4503" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4504" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4504" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4504" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4504">
+        <v>4202</v>
+      </c>
+      <c r="D4504">
+        <v>14400</v>
+      </c>
+      <c r="E4504" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4505" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4505" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4505">
+        <v>4010</v>
+      </c>
+      <c r="D4505">
+        <v>8000</v>
+      </c>
+      <c r="E4505" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4506" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4506" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4506" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4506">
+        <v>3922</v>
+      </c>
+      <c r="D4506">
+        <v>8000</v>
+      </c>
+      <c r="E4506" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4507" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4507" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4507" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4507">
+        <v>3540</v>
+      </c>
+      <c r="D4507">
+        <v>8000</v>
+      </c>
+      <c r="E4507" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4508" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4508" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4508" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4508">
+        <v>3540</v>
+      </c>
+      <c r="D4508">
+        <v>8000</v>
+      </c>
+      <c r="E4508" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4509" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4509" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4509" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4509">
+        <v>3402</v>
+      </c>
+      <c r="D4509">
+        <v>8000</v>
+      </c>
+      <c r="E4509" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4510" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4510" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4510" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4510">
+        <v>3364</v>
+      </c>
+      <c r="D4510">
+        <v>8000</v>
+      </c>
+      <c r="E4510" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4511" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4511" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4511" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4511">
+        <v>3358</v>
+      </c>
+      <c r="D4511">
+        <v>8000</v>
+      </c>
+      <c r="E4511" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4512" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4512" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4512" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4512">
+        <v>3196</v>
+      </c>
+      <c r="D4512">
+        <v>3500</v>
+      </c>
+      <c r="E4512" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4513" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4513" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4513" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4513">
+        <v>2988</v>
+      </c>
+      <c r="D4513">
+        <v>8000</v>
+      </c>
+      <c r="E4513" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4514" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4514" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4514" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4514">
+        <v>2988</v>
+      </c>
+      <c r="D4514">
+        <v>8000</v>
+      </c>
+      <c r="E4514" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4515" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4515" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4515" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4515">
+        <v>1988</v>
+      </c>
+      <c r="D4515">
+        <v>2500</v>
+      </c>
+      <c r="E4515" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4516" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4516" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4516" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4516">
+        <v>1000</v>
+      </c>
+      <c r="D4516">
+        <v>2400</v>
+      </c>
+      <c r="E4516" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4517" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4517" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B4517" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4517">
+        <v>484</v>
+      </c>
+      <c r="D4517">
+        <v>15200</v>
+      </c>
+      <c r="E4517" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4518" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4518" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4518" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4518">
+        <v>3864</v>
+      </c>
+      <c r="D4518">
+        <v>8000</v>
+      </c>
+      <c r="E4518" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4519" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4519" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4519" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4519">
+        <v>2478</v>
+      </c>
+      <c r="D4519">
+        <v>4000</v>
+      </c>
+      <c r="E4519" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4520" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4520" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4520" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4520">
+        <v>4327</v>
+      </c>
+      <c r="D4520">
+        <v>8000</v>
+      </c>
+      <c r="E4520" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4521" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4521" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4521" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4521">
+        <v>3800</v>
+      </c>
+      <c r="D4521">
+        <v>8000</v>
+      </c>
+      <c r="E4521" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4522" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4522" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4522" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4522">
+        <v>2823</v>
+      </c>
+      <c r="D4522">
+        <v>8000</v>
+      </c>
+      <c r="E4522" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4523" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4523" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4523" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4523">
+        <v>3876</v>
+      </c>
+      <c r="D4523">
+        <v>8000</v>
+      </c>
+      <c r="E4523" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4524" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4524" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4524" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4524">
+        <v>3616</v>
+      </c>
+      <c r="D4524">
+        <v>8000</v>
+      </c>
+      <c r="E4524" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4525" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4525" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4525" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4525">
+        <v>3338</v>
+      </c>
+      <c r="D4525">
+        <v>8000</v>
+      </c>
+      <c r="E4525" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4526" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4526" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4526" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4526">
+        <v>3400</v>
+      </c>
+      <c r="D4526">
+        <v>8000</v>
+      </c>
+      <c r="E4526" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4527" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4527" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4527" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4527">
+        <v>197</v>
+      </c>
+      <c r="D4527">
+        <v>7200</v>
+      </c>
+      <c r="E4527" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4528" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4528" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4528" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4528">
+        <v>1556</v>
+      </c>
+      <c r="D4528">
+        <v>2400</v>
+      </c>
+      <c r="E4528" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4529" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4529" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4529" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4529">
+        <v>4235</v>
+      </c>
+      <c r="D4529">
+        <v>8000</v>
+      </c>
+      <c r="E4529" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4530" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4530" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4530" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4530">
+        <v>4332</v>
+      </c>
+      <c r="D4530">
+        <v>12000</v>
+      </c>
+      <c r="E4530" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4531" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4531" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4531" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4531">
+        <v>3884</v>
+      </c>
+      <c r="D4531">
+        <v>100000</v>
+      </c>
+      <c r="E4531" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4532" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4532" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4532" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4532">
+        <v>3630</v>
+      </c>
+      <c r="D4532">
+        <v>8000</v>
+      </c>
+      <c r="E4532" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4533" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4533" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4533" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4533">
+        <v>6188</v>
+      </c>
+      <c r="D4533">
+        <v>13500</v>
+      </c>
+      <c r="E4533" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4534" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4534" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4534" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4534">
+        <v>4809</v>
+      </c>
+      <c r="D4534">
+        <v>4750</v>
+      </c>
+      <c r="E4534" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4535" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4535" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4535" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4535">
+        <v>8088</v>
+      </c>
+      <c r="D4535">
+        <v>8000</v>
+      </c>
+      <c r="E4535" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4536" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4536" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4536" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4536">
+        <v>13571</v>
+      </c>
+      <c r="D4536">
+        <v>17250</v>
+      </c>
+      <c r="E4536" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4537" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4537" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4537" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4537">
+        <v>2212</v>
+      </c>
+      <c r="D4537">
+        <v>2000</v>
+      </c>
+      <c r="E4537" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4538" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4538" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4538" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4538">
+        <v>5060</v>
+      </c>
+      <c r="D4538">
+        <v>5000</v>
+      </c>
+      <c r="E4538" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4539" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4539" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4539" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4539">
+        <v>12604</v>
+      </c>
+      <c r="D4539">
+        <v>13500</v>
+      </c>
+      <c r="E4539" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4540" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4540" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4540" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4540">
+        <v>6436</v>
+      </c>
+      <c r="D4540">
+        <v>7000</v>
+      </c>
+      <c r="E4540" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4541" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4541" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B4541" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4541">
+        <v>6736</v>
+      </c>
+      <c r="D4541">
+        <v>6500</v>
+      </c>
+      <c r="E4541" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4542" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4542" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4542" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4542">
+        <v>5307</v>
+      </c>
+      <c r="D4542">
+        <v>99000</v>
+      </c>
+      <c r="E4542" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4543" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4543" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4543" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4543">
+        <v>4273</v>
+      </c>
+      <c r="D4543">
+        <v>9000</v>
+      </c>
+      <c r="E4543" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4544" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4544" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4544" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4544">
+        <v>4219</v>
+      </c>
+      <c r="D4544">
+        <v>9000</v>
+      </c>
+      <c r="E4544" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4545" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4545" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4545">
+        <v>4039</v>
+      </c>
+      <c r="D4545">
+        <v>9000</v>
+      </c>
+      <c r="E4545" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4546" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4546" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4546" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4546">
+        <v>3945</v>
+      </c>
+      <c r="D4546">
+        <v>9000</v>
+      </c>
+      <c r="E4546" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4547" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4547" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4547">
+        <v>3840</v>
+      </c>
+      <c r="D4547">
+        <v>9000</v>
+      </c>
+      <c r="E4547" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4548" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4548" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4548">
+        <v>3837</v>
+      </c>
+      <c r="D4548">
+        <v>9000</v>
+      </c>
+      <c r="E4548" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4549" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4549" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4549">
+        <v>3826</v>
+      </c>
+      <c r="D4549">
+        <v>2750</v>
+      </c>
+      <c r="E4549" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4550" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4550" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4550">
+        <v>3826</v>
+      </c>
+      <c r="D4550">
+        <v>2750</v>
+      </c>
+      <c r="E4550" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4551" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4551" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4551">
+        <v>3820</v>
+      </c>
+      <c r="D4551">
+        <v>9000</v>
+      </c>
+      <c r="E4551" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4552" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4552" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4552">
+        <v>3716</v>
+      </c>
+      <c r="D4552">
+        <v>9000</v>
+      </c>
+      <c r="E4552" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4553" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4553" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4553">
+        <v>3635</v>
+      </c>
+      <c r="D4553">
+        <v>22500</v>
+      </c>
+      <c r="E4553" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4554" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4554" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4554">
+        <v>3378</v>
+      </c>
+      <c r="D4554">
+        <v>9000</v>
+      </c>
+      <c r="E4554" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4555" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4555" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4555" t="s">
+        <v>347</v>
+      </c>
+      <c r="C4555">
+        <v>2600</v>
+      </c>
+      <c r="D4555">
+        <v>9000</v>
+      </c>
+      <c r="E4555" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4556" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4556" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4556">
+        <v>2478</v>
+      </c>
+      <c r="D4556">
+        <v>4500</v>
+      </c>
+      <c r="E4556" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4557" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4557" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4557">
+        <v>2424</v>
+      </c>
+      <c r="D4557">
+        <v>2000</v>
+      </c>
+      <c r="E4557" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4558" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4558" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4558" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4558">
+        <v>2424</v>
+      </c>
+      <c r="D4558">
+        <v>2000</v>
+      </c>
+      <c r="E4558" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4559" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4559" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4559" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4559">
+        <v>1096</v>
+      </c>
+      <c r="D4559">
+        <v>2700</v>
+      </c>
+      <c r="E4559" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4560" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4560" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B4560" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4560">
+        <v>189</v>
+      </c>
+      <c r="D4560">
+        <v>8100</v>
+      </c>
+      <c r="E4560" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4561" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4561" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4561" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4561">
+        <v>11086</v>
+      </c>
+      <c r="D4561">
+        <v>13000</v>
+      </c>
+      <c r="E4561" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4562" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4562" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4562" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4562">
+        <v>10692</v>
+      </c>
+      <c r="D4562">
+        <v>12750</v>
+      </c>
+      <c r="E4562" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4563" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4563" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4563" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4563">
+        <v>8638</v>
+      </c>
+      <c r="D4563">
+        <v>10500</v>
+      </c>
+      <c r="E4563" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4564" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4564" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4564" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4564">
+        <v>7861</v>
+      </c>
+      <c r="D4564">
+        <v>8300</v>
+      </c>
+      <c r="E4564" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4565" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4565" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4565" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4565">
+        <v>6664</v>
+      </c>
+      <c r="D4565">
+        <v>7000</v>
+      </c>
+      <c r="E4565" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4566" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4566" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4566" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4566">
+        <v>6274</v>
+      </c>
+      <c r="D4566">
+        <v>4500</v>
+      </c>
+      <c r="E4566" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4567" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4567" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4567" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4567">
+        <v>5310</v>
+      </c>
+      <c r="D4567">
+        <v>4500</v>
+      </c>
+      <c r="E4567" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4568" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4568" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4568" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4568">
+        <v>4456</v>
+      </c>
+      <c r="D4568">
+        <v>4500</v>
+      </c>
+      <c r="E4568" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4569" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4569" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4569" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4569">
+        <v>4123</v>
+      </c>
+      <c r="D4569">
+        <v>8000</v>
+      </c>
+      <c r="E4569" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4570" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4570" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4570" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4570">
+        <v>3914</v>
+      </c>
+      <c r="D4570">
+        <v>8000</v>
+      </c>
+      <c r="E4570" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4571" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4571" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4571" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4571">
+        <v>3788</v>
+      </c>
+      <c r="D4571">
+        <v>8000</v>
+      </c>
+      <c r="E4571" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4572" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4572" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4572" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4572">
+        <v>3758</v>
+      </c>
+      <c r="D4572">
+        <v>2500</v>
+      </c>
+      <c r="E4572" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4573" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4573" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4573" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4573">
+        <v>3700</v>
+      </c>
+      <c r="D4573">
+        <v>8000</v>
+      </c>
+      <c r="E4573" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4574" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4574" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4574" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4574">
+        <v>3475</v>
+      </c>
+      <c r="D4574">
+        <v>24000</v>
+      </c>
+      <c r="E4574" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4575" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4575" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4575" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4575">
+        <v>3456</v>
+      </c>
+      <c r="D4575">
+        <v>3500</v>
+      </c>
+      <c r="E4575" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4576" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4576" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4576" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4576">
+        <v>3441</v>
+      </c>
+      <c r="D4576">
+        <v>8000</v>
+      </c>
+      <c r="E4576" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4577" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4577" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4577" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4577">
+        <v>3441</v>
+      </c>
+      <c r="D4577">
+        <v>8000</v>
+      </c>
+      <c r="E4577" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4578" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4578" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4578" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4578">
+        <v>3394</v>
+      </c>
+      <c r="D4578">
+        <v>8000</v>
+      </c>
+      <c r="E4578" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4579" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4579" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4579" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4579">
+        <v>3390</v>
+      </c>
+      <c r="D4579">
+        <v>8000</v>
+      </c>
+      <c r="E4579" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4580" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4580" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4580" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4580">
+        <v>3167</v>
+      </c>
+      <c r="D4580">
+        <v>8000</v>
+      </c>
+      <c r="E4580" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4581" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4581" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4581" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4581">
+        <v>2980</v>
+      </c>
+      <c r="D4581">
+        <v>4000</v>
+      </c>
+      <c r="E4581" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4582" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4582" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4582" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4582">
+        <v>2794</v>
+      </c>
+      <c r="D4582">
+        <v>2500</v>
+      </c>
+      <c r="E4582" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4583" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4583" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4583" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4583">
+        <v>2638</v>
+      </c>
+      <c r="D4583">
+        <v>8000</v>
+      </c>
+      <c r="E4583" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4584" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4584" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4584" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4584">
+        <v>2256</v>
+      </c>
+      <c r="D4584">
+        <v>2400</v>
+      </c>
+      <c r="E4584" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4585" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4585" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4585" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4585">
+        <v>2072</v>
+      </c>
+      <c r="D4585">
+        <v>2250</v>
+      </c>
+      <c r="E4585" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4586" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4586" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4586" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4586">
+        <v>1348</v>
+      </c>
+      <c r="D4586">
+        <v>1500</v>
+      </c>
+      <c r="E4586" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4587" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4587" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B4587" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4587">
+        <v>218</v>
+      </c>
+      <c r="D4587">
+        <v>7200</v>
+      </c>
+      <c r="E4587" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4588" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4588" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4588" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4588">
+        <v>16101</v>
+      </c>
+      <c r="D4588">
+        <v>19500</v>
+      </c>
+      <c r="E4588" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4589" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4589" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4589" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4589">
+        <v>13713</v>
+      </c>
+      <c r="D4589">
+        <v>17500</v>
+      </c>
+      <c r="E4589" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4590" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4590" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4590" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4590">
+        <v>10480</v>
+      </c>
+      <c r="D4590">
+        <v>9000</v>
+      </c>
+      <c r="E4590" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4591" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4591" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4591" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4591">
+        <v>8696</v>
+      </c>
+      <c r="D4591">
+        <v>8500</v>
+      </c>
+      <c r="E4591" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4592" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4592" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4592" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4592">
+        <v>7479</v>
+      </c>
+      <c r="D4592">
+        <v>4500</v>
+      </c>
+      <c r="E4592" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4593" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4593" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4593" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4593">
+        <v>6761</v>
+      </c>
+      <c r="D4593">
+        <v>4250</v>
+      </c>
+      <c r="E4593" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4594" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4594" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4594" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4594">
+        <v>6177</v>
+      </c>
+      <c r="D4594">
+        <v>92700</v>
+      </c>
+      <c r="E4594" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4595" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4595" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4595" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4595">
+        <v>6176</v>
+      </c>
+      <c r="D4595">
+        <v>6000</v>
+      </c>
+      <c r="E4595" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4596" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4596" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4596" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4596">
+        <v>5896</v>
+      </c>
+      <c r="D4596">
+        <v>4250</v>
+      </c>
+      <c r="E4596" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4597" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4597" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4597" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4597">
+        <v>5896</v>
+      </c>
+      <c r="D4597">
+        <v>4250</v>
+      </c>
+      <c r="E4597" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4598" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4598" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4598" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4598">
+        <v>5859</v>
+      </c>
+      <c r="D4598">
+        <v>4250</v>
+      </c>
+      <c r="E4598" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4599" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4599" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4599" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4599">
+        <v>5584</v>
+      </c>
+      <c r="D4599">
+        <v>4000</v>
+      </c>
+      <c r="E4599" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4600" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4600" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4600" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4600">
+        <v>5584</v>
+      </c>
+      <c r="D4600">
+        <v>4000</v>
+      </c>
+      <c r="E4600" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4601" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4601" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4601" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4601">
+        <v>5546</v>
+      </c>
+      <c r="D4601">
+        <v>5750</v>
+      </c>
+      <c r="E4601" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4602" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4602" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4602" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4602">
+        <v>5241</v>
+      </c>
+      <c r="D4602">
+        <v>4000</v>
+      </c>
+      <c r="E4602" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4603" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4603" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4603" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4603">
+        <v>4638</v>
+      </c>
+      <c r="D4603">
+        <v>9000</v>
+      </c>
+      <c r="E4603" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4604" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4604" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4604">
+        <v>4530</v>
+      </c>
+      <c r="D4604">
+        <v>31500</v>
+      </c>
+      <c r="E4604" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4605" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4605" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4605" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4605">
+        <v>4465</v>
+      </c>
+      <c r="D4605">
+        <v>9000</v>
+      </c>
+      <c r="E4605" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4606" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4606" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4606">
+        <v>4256</v>
+      </c>
+      <c r="D4606">
+        <v>4500</v>
+      </c>
+      <c r="E4606" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4607" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4607" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4607">
+        <v>4141</v>
+      </c>
+      <c r="D4607">
+        <v>4000</v>
+      </c>
+      <c r="E4607" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4608" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4608" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4608">
+        <v>4051</v>
+      </c>
+      <c r="D4608">
+        <v>9000</v>
+      </c>
+      <c r="E4608" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4609" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4609" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4609">
+        <v>4021</v>
+      </c>
+      <c r="D4609">
+        <v>9000</v>
+      </c>
+      <c r="E4609" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4610" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4610" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4610">
+        <v>3981</v>
+      </c>
+      <c r="D4610">
+        <v>4000</v>
+      </c>
+      <c r="E4610" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4611" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4611" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4611">
+        <v>3981</v>
+      </c>
+      <c r="D4611">
+        <v>4000</v>
+      </c>
+      <c r="E4611" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4612" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4612" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4612">
+        <v>3966</v>
+      </c>
+      <c r="D4612">
+        <v>9000</v>
+      </c>
+      <c r="E4612" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4613" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4613" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4613">
+        <v>3830</v>
+      </c>
+      <c r="D4613">
+        <v>9000</v>
+      </c>
+      <c r="E4613" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4614" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4614" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4614" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4614">
+        <v>3661</v>
+      </c>
+      <c r="D4614">
+        <v>9000</v>
+      </c>
+      <c r="E4614" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4615" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4615" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4615" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4615">
+        <v>3521</v>
+      </c>
+      <c r="D4615">
+        <v>9000</v>
+      </c>
+      <c r="E4615" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4616" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4616" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4616" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4616">
+        <v>3370</v>
+      </c>
+      <c r="D4616">
+        <v>9000</v>
+      </c>
+      <c r="E4616" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4617" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4617" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4617" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4617">
+        <v>3273</v>
+      </c>
+      <c r="D4617">
+        <v>4000</v>
+      </c>
+      <c r="E4617" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4618" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4618" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4618" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4618">
+        <v>3273</v>
+      </c>
+      <c r="D4618">
+        <v>4000</v>
+      </c>
+      <c r="E4618" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4619" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4619" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4619" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4619">
+        <v>2938</v>
+      </c>
+      <c r="D4619">
+        <v>9000</v>
+      </c>
+      <c r="E4619" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4620" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4620" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4620" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4620">
+        <v>2922</v>
+      </c>
+      <c r="D4620">
+        <v>2500</v>
+      </c>
+      <c r="E4620" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4621" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4621" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4621" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4621">
+        <v>2922</v>
+      </c>
+      <c r="D4621">
+        <v>2500</v>
+      </c>
+      <c r="E4621" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4622" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4622" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4622" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4622">
+        <v>2809</v>
+      </c>
+      <c r="D4622">
+        <v>2500</v>
+      </c>
+      <c r="E4622" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4623" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4623" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4623" t="s">
+        <v>347</v>
+      </c>
+      <c r="C4623">
+        <v>2357</v>
+      </c>
+      <c r="D4623">
+        <v>9000</v>
+      </c>
+      <c r="E4623" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4624" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4624" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4624" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4624">
+        <v>2284</v>
+      </c>
+      <c r="D4624">
+        <v>7200</v>
+      </c>
+      <c r="E4624" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4625" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4625" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4625">
+        <v>1478</v>
+      </c>
+      <c r="D4625">
+        <v>4500</v>
+      </c>
+      <c r="E4625" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4626" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4626" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4626">
+        <v>946</v>
+      </c>
+      <c r="D4626">
+        <v>1000</v>
+      </c>
+      <c r="E4626" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4627" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4627" t="s">
+        <v>408</v>
+      </c>
+      <c r="C4627">
+        <v>220</v>
+      </c>
+      <c r="D4627">
+        <v>4500</v>
+      </c>
+      <c r="E4627" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4628" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4628" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B4628" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4628">
+        <v>217</v>
+      </c>
+      <c r="D4628">
+        <v>8100</v>
+      </c>
+      <c r="E4628" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4629" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4629" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4629" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4629">
+        <v>13173</v>
+      </c>
+      <c r="D4629">
+        <v>14500</v>
+      </c>
+      <c r="E4629" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4630" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4630" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4630" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4630">
+        <v>9049</v>
+      </c>
+      <c r="D4630">
+        <v>10500</v>
+      </c>
+      <c r="E4630" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4631" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4631" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4631" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4631">
+        <v>7892</v>
+      </c>
+      <c r="D4631">
+        <v>5500</v>
+      </c>
+      <c r="E4631" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4632" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4632" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4632">
+        <v>6897</v>
+      </c>
+      <c r="D4632">
+        <v>4000</v>
+      </c>
+      <c r="E4632" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4633" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4633" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4633">
+        <v>6897</v>
+      </c>
+      <c r="D4633">
+        <v>4000</v>
+      </c>
+      <c r="E4633" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4634" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4634" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4634">
+        <v>6624</v>
+      </c>
+      <c r="D4634">
+        <v>7000</v>
+      </c>
+      <c r="E4634" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4635" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4635" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4635">
+        <v>5856</v>
+      </c>
+      <c r="D4635">
+        <v>6000</v>
+      </c>
+      <c r="E4635" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4636" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4636" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4636">
+        <v>5856</v>
+      </c>
+      <c r="D4636">
+        <v>6000</v>
+      </c>
+      <c r="E4636" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4637" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4637" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4637">
+        <v>5672</v>
+      </c>
+      <c r="D4637">
+        <v>3500</v>
+      </c>
+      <c r="E4637" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4638" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4638" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4638">
+        <v>5672</v>
+      </c>
+      <c r="D4638">
+        <v>3500</v>
+      </c>
+      <c r="E4638" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4639" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4639" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4639">
+        <v>5672</v>
+      </c>
+      <c r="D4639">
+        <v>3500</v>
+      </c>
+      <c r="E4639" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4640" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4640" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4640">
+        <v>5672</v>
+      </c>
+      <c r="D4640">
+        <v>3500</v>
+      </c>
+      <c r="E4640" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4641" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4641" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4641" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4641">
+        <v>5532</v>
+      </c>
+      <c r="D4641">
+        <v>5500</v>
+      </c>
+      <c r="E4641" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4642" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4642" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4642">
+        <v>5410</v>
+      </c>
+      <c r="D4642">
+        <v>4000</v>
+      </c>
+      <c r="E4642" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4643" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4643" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4643">
+        <v>5292</v>
+      </c>
+      <c r="D4643">
+        <v>5500</v>
+      </c>
+      <c r="E4643" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4644" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4644" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4644">
+        <v>5212</v>
+      </c>
+      <c r="D4644">
+        <v>4500</v>
+      </c>
+      <c r="E4644" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4645" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4645" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4645">
+        <v>4889</v>
+      </c>
+      <c r="D4645">
+        <v>5000</v>
+      </c>
+      <c r="E4645" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4646" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4646" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4646">
+        <v>4784</v>
+      </c>
+      <c r="D4646">
+        <v>4500</v>
+      </c>
+      <c r="E4646" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4647" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4647" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4647">
+        <v>3959</v>
+      </c>
+      <c r="D4647">
+        <v>4250</v>
+      </c>
+      <c r="E4647" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4648" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4648" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4648">
+        <v>3959</v>
+      </c>
+      <c r="D4648">
+        <v>4250</v>
+      </c>
+      <c r="E4648" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4649" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4649" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4649">
+        <v>3918</v>
+      </c>
+      <c r="D4649">
+        <v>88000</v>
+      </c>
+      <c r="E4649" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4650" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4650" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4650">
+        <v>3801</v>
+      </c>
+      <c r="D4650">
+        <v>8000</v>
+      </c>
+      <c r="E4650" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4651" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4651" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4651">
+        <v>3629</v>
+      </c>
+      <c r="D4651">
+        <v>8000</v>
+      </c>
+      <c r="E4651" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4652" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4652" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4652">
+        <v>3430</v>
+      </c>
+      <c r="D4652">
+        <v>8000</v>
+      </c>
+      <c r="E4652" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4653" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4653" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4653">
+        <v>3353</v>
+      </c>
+      <c r="D4653">
+        <v>8000</v>
+      </c>
+      <c r="E4653" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4654" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4654" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4654">
+        <v>3314</v>
+      </c>
+      <c r="D4654">
+        <v>3750</v>
+      </c>
+      <c r="E4654" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4655" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4655" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4655" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4655">
+        <v>3314</v>
+      </c>
+      <c r="D4655">
+        <v>3750</v>
+      </c>
+      <c r="E4655" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4656" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4656" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4656">
+        <v>3239</v>
+      </c>
+      <c r="D4656">
+        <v>8000</v>
+      </c>
+      <c r="E4656" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4657" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4657" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4657" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4657">
+        <v>3239</v>
+      </c>
+      <c r="D4657">
+        <v>8000</v>
+      </c>
+      <c r="E4657" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4658" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4658" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4658" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4658">
+        <v>3230</v>
+      </c>
+      <c r="D4658">
+        <v>8000</v>
+      </c>
+      <c r="E4658" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4659" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4659" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4659" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4659">
+        <v>3190</v>
+      </c>
+      <c r="D4659">
+        <v>8000</v>
+      </c>
+      <c r="E4659" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4660" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4660" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4660" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4660">
+        <v>3160</v>
+      </c>
+      <c r="D4660">
+        <v>8000</v>
+      </c>
+      <c r="E4660" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4661" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4661" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4661" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4661">
+        <v>2890</v>
+      </c>
+      <c r="D4661">
+        <v>4000</v>
+      </c>
+      <c r="E4661" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4662" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4662" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4662" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4662">
+        <v>2775</v>
+      </c>
+      <c r="D4662">
+        <v>4000</v>
+      </c>
+      <c r="E4662" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4663" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4663" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4663" t="s">
+        <v>409</v>
+      </c>
+      <c r="C4663">
+        <v>2317</v>
+      </c>
+      <c r="D4663">
+        <v>2000</v>
+      </c>
+      <c r="E4663" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4664" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4664" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4664" t="s">
+        <v>410</v>
+      </c>
+      <c r="C4664">
+        <v>2010</v>
+      </c>
+      <c r="D4664">
+        <v>2500</v>
+      </c>
+      <c r="E4664" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4665" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4665" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4665" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4665">
+        <v>1902</v>
+      </c>
+      <c r="D4665">
+        <v>2000</v>
+      </c>
+      <c r="E4665" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4666" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4666" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4666" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4666">
+        <v>1068</v>
+      </c>
+      <c r="D4666">
+        <v>2400</v>
+      </c>
+      <c r="E4666" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4667" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4667" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B4667" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4667">
+        <v>201</v>
+      </c>
+      <c r="D4667">
+        <v>7200</v>
+      </c>
+      <c r="E4667" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4668" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4668" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4668" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4668">
+        <v>9503</v>
+      </c>
+      <c r="D4668">
+        <v>80750</v>
+      </c>
+      <c r="E4668" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4669" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4669" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4669" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4669">
+        <v>7889</v>
+      </c>
+      <c r="D4669">
+        <v>5500</v>
+      </c>
+      <c r="E4669" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4670" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4670" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4670" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4670">
+        <v>6979</v>
+      </c>
+      <c r="D4670">
+        <v>19000</v>
+      </c>
+      <c r="E4670" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4671" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4671" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4671">
+        <v>6241</v>
+      </c>
+      <c r="D4671">
+        <v>4000</v>
+      </c>
+      <c r="E4671" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4672" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4672" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4672" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4672">
+        <v>6241</v>
+      </c>
+      <c r="D4672">
+        <v>4000</v>
+      </c>
+      <c r="E4672" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4673" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4673" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4673" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4673">
+        <v>6086</v>
+      </c>
+      <c r="D4673">
+        <v>4500</v>
+      </c>
+      <c r="E4673" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4674" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4674" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4674" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4674">
+        <v>5486</v>
+      </c>
+      <c r="D4674">
+        <v>4000</v>
+      </c>
+      <c r="E4674" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4675" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4675" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4675" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4675">
+        <v>5245</v>
+      </c>
+      <c r="D4675">
+        <v>4500</v>
+      </c>
+      <c r="E4675" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4676" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4676" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4676" t="s">
+        <v>413</v>
+      </c>
+      <c r="C4676">
+        <v>5245</v>
+      </c>
+      <c r="D4676">
+        <v>4000</v>
+      </c>
+      <c r="E4676" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4677" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4677" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4677" t="s">
+        <v>414</v>
+      </c>
+      <c r="C4677">
+        <v>5245</v>
+      </c>
+      <c r="D4677">
+        <v>4000</v>
+      </c>
+      <c r="E4677" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4678" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4678" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4678" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4678">
+        <v>5245</v>
+      </c>
+      <c r="D4678">
+        <v>4000</v>
+      </c>
+      <c r="E4678" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4679" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4679" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4679" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4679">
+        <v>4433</v>
+      </c>
+      <c r="D4679">
+        <v>3500</v>
+      </c>
+      <c r="E4679" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4680" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4680" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4680">
+        <v>4178</v>
+      </c>
+      <c r="D4680">
+        <v>4750</v>
+      </c>
+      <c r="E4680" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4681" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4681" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4681" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4681">
+        <v>4174</v>
+      </c>
+      <c r="D4681">
+        <v>4000</v>
+      </c>
+      <c r="E4681" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4682" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4682" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4682" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4682">
+        <v>3978</v>
+      </c>
+      <c r="D4682">
+        <v>4750</v>
+      </c>
+      <c r="E4682" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4683" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4683" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4683" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4683">
+        <v>3978</v>
+      </c>
+      <c r="D4683">
+        <v>4750</v>
+      </c>
+      <c r="E4683" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4684" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4684" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4684" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4684">
+        <v>3957</v>
+      </c>
+      <c r="D4684">
+        <v>4750</v>
+      </c>
+      <c r="E4684" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4685" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4685" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4685" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4685">
+        <v>3957</v>
+      </c>
+      <c r="D4685">
+        <v>4000</v>
+      </c>
+      <c r="E4685" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4686" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4686" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4686" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4686">
+        <v>3887</v>
+      </c>
+      <c r="D4686">
+        <v>4500</v>
+      </c>
+      <c r="E4686" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4687" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4687" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4687">
+        <v>3887</v>
+      </c>
+      <c r="D4687">
+        <v>4750</v>
+      </c>
+      <c r="E4687" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4688" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4688" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4688" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4688">
+        <v>3850</v>
+      </c>
+      <c r="D4688">
+        <v>4750</v>
+      </c>
+      <c r="E4688" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4689" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4689" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4689" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4689">
+        <v>3637</v>
+      </c>
+      <c r="D4689">
+        <v>4000</v>
+      </c>
+      <c r="E4689" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4690" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4690" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4690" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4690">
+        <v>3637</v>
+      </c>
+      <c r="D4690">
+        <v>4000</v>
+      </c>
+      <c r="E4690" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4691" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4691" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4691" t="s">
+        <v>415</v>
+      </c>
+      <c r="C4691">
+        <v>3597</v>
+      </c>
+      <c r="D4691">
+        <v>9500</v>
+      </c>
+      <c r="E4691" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4692" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4692" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4692">
+        <v>3581</v>
+      </c>
+      <c r="D4692">
+        <v>9500</v>
+      </c>
+      <c r="E4692" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4693" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4693" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4693">
+        <v>3247</v>
+      </c>
+      <c r="D4693">
+        <v>4000</v>
+      </c>
+      <c r="E4693" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4694" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4694" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4694">
+        <v>3246</v>
+      </c>
+      <c r="D4694">
+        <v>3500</v>
+      </c>
+      <c r="E4694" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4695" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4695" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4695">
+        <v>3193</v>
+      </c>
+      <c r="D4695">
+        <v>4000</v>
+      </c>
+      <c r="E4695" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4696" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4696" t="s">
+        <v>416</v>
+      </c>
+      <c r="C4696">
+        <v>3072</v>
+      </c>
+      <c r="D4696">
+        <v>2500</v>
+      </c>
+      <c r="E4696" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4697" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4697" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4697">
+        <v>3035</v>
+      </c>
+      <c r="D4697">
+        <v>4000</v>
+      </c>
+      <c r="E4697" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4698" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4698" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4698">
+        <v>2639</v>
+      </c>
+      <c r="D4698">
+        <v>3250</v>
+      </c>
+      <c r="E4698" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4699" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4699" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4699" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4699">
+        <v>2481</v>
+      </c>
+      <c r="D4699">
+        <v>9500</v>
+      </c>
+      <c r="E4699" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4700" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4700" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4700" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4700">
+        <v>2278</v>
+      </c>
+      <c r="D4700">
+        <v>4750</v>
+      </c>
+      <c r="E4700" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4701" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4701" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4701" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4701">
+        <v>2260</v>
+      </c>
+      <c r="D4701">
+        <v>2000</v>
+      </c>
+      <c r="E4701" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4702" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4702" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4702">
+        <v>2260</v>
+      </c>
+      <c r="D4702">
+        <v>2000</v>
+      </c>
+      <c r="E4702" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4703" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4703" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4703">
+        <v>2044</v>
+      </c>
+      <c r="D4703">
+        <v>2000</v>
+      </c>
+      <c r="E4703" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4704" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4704" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4704">
+        <v>1834</v>
+      </c>
+      <c r="D4704">
+        <v>14250</v>
+      </c>
+      <c r="E4704" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4705" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4705" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4705" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4705">
+        <v>1364</v>
+      </c>
+      <c r="D4705">
+        <v>1500</v>
+      </c>
+      <c r="E4705" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4706" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4706" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B4706" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4706">
+        <v>197</v>
+      </c>
+      <c r="D4706">
+        <v>8550</v>
+      </c>
+      <c r="E4706" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4707" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4707" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4707" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4707">
+        <v>14533</v>
+      </c>
+      <c r="D4707">
+        <v>15000</v>
+      </c>
+      <c r="E4707" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4708" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4708" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4708" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4708">
+        <v>13086</v>
+      </c>
+      <c r="D4708">
+        <v>14000</v>
+      </c>
+      <c r="E4708" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4709" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4709" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4709" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4709">
+        <v>11651</v>
+      </c>
+      <c r="D4709">
+        <v>12000</v>
+      </c>
+      <c r="E4709" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4710" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4710" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4710" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4710">
+        <v>9428</v>
+      </c>
+      <c r="D4710">
+        <v>8000</v>
+      </c>
+      <c r="E4710" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4711" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4711" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4711" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4711">
+        <v>6166</v>
+      </c>
+      <c r="D4711">
+        <v>6000</v>
+      </c>
+      <c r="E4711" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4712" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4712" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4712" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4712">
+        <v>6028</v>
+      </c>
+      <c r="D4712">
+        <v>5500</v>
+      </c>
+      <c r="E4712" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4713" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4713" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4713" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4713">
+        <v>5652</v>
+      </c>
+      <c r="D4713">
+        <v>3500</v>
+      </c>
+      <c r="E4713" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4714" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4714" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4714" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4714">
+        <v>5652</v>
+      </c>
+      <c r="D4714">
+        <v>3500</v>
+      </c>
+      <c r="E4714" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4715" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4715" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4715" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4715">
+        <v>5023</v>
+      </c>
+      <c r="D4715">
+        <v>3500</v>
+      </c>
+      <c r="E4715" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4716" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4716" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4716" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4716">
+        <v>4555</v>
+      </c>
+      <c r="D4716">
+        <v>3500</v>
+      </c>
+      <c r="E4716" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4717" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4717" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4717" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4717">
+        <v>4452</v>
+      </c>
+      <c r="D4717">
+        <v>2000</v>
+      </c>
+      <c r="E4717" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4718" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4718" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4718" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4718">
+        <v>3920</v>
+      </c>
+      <c r="D4718">
+        <v>8000</v>
+      </c>
+      <c r="E4718" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4719" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4719" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4719" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4719">
+        <v>3601</v>
+      </c>
+      <c r="D4719">
+        <v>20000</v>
+      </c>
+      <c r="E4719" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4720" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4720" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4720" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4720">
+        <v>3582</v>
+      </c>
+      <c r="D4720">
+        <v>3750</v>
+      </c>
+      <c r="E4720" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4721" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4721" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4721" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4721">
+        <v>3582</v>
+      </c>
+      <c r="D4721">
+        <v>3750</v>
+      </c>
+      <c r="E4721" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4722" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4722" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4722">
+        <v>3555</v>
+      </c>
+      <c r="D4722">
+        <v>8000</v>
+      </c>
+      <c r="E4722" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4723" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4723" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4723" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4723">
+        <v>3464</v>
+      </c>
+      <c r="D4723">
+        <v>3500</v>
+      </c>
+      <c r="E4723" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4724" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4724" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4724">
+        <v>3464</v>
+      </c>
+      <c r="D4724">
+        <v>3500</v>
+      </c>
+      <c r="E4724" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4725" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4725" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4725">
+        <v>3164</v>
+      </c>
+      <c r="D4725">
+        <v>8000</v>
+      </c>
+      <c r="E4725" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4726" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4726" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4726">
+        <v>3144</v>
+      </c>
+      <c r="D4726">
+        <v>8000</v>
+      </c>
+      <c r="E4726" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4727" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4727">
+        <v>3128</v>
+      </c>
+      <c r="D4727">
+        <v>3500</v>
+      </c>
+      <c r="E4727" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4728" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4728" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4728">
+        <v>3056</v>
+      </c>
+      <c r="D4728">
+        <v>6400</v>
+      </c>
+      <c r="E4728" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4729" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4729" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4729" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4729">
+        <v>2880</v>
+      </c>
+      <c r="D4729">
+        <v>3500</v>
+      </c>
+      <c r="E4729" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4730" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4730" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4730" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4730">
+        <v>2654</v>
+      </c>
+      <c r="D4730">
+        <v>4000</v>
+      </c>
+      <c r="E4730" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4731" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4731" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4731" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4731">
+        <v>2654</v>
+      </c>
+      <c r="D4731">
+        <v>4000</v>
+      </c>
+      <c r="E4731" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4732" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4732" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4732" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4732">
+        <v>2580</v>
+      </c>
+      <c r="D4732">
+        <v>2500</v>
+      </c>
+      <c r="E4732" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4733" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4733" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4733" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4733">
+        <v>2523</v>
+      </c>
+      <c r="D4733">
+        <v>4000</v>
+      </c>
+      <c r="E4733" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4734" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4734" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4734" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4734">
+        <v>2416</v>
+      </c>
+      <c r="D4734">
+        <v>4000</v>
+      </c>
+      <c r="E4734" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4735" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4735" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4735" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4735">
+        <v>2406</v>
+      </c>
+      <c r="D4735">
+        <v>4000</v>
+      </c>
+      <c r="E4735" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4736" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4736" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4736" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4736">
+        <v>2214</v>
+      </c>
+      <c r="D4736">
+        <v>3000</v>
+      </c>
+      <c r="E4736" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4737" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4737" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4737" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4737">
+        <v>2211</v>
+      </c>
+      <c r="D4737">
+        <v>4000</v>
+      </c>
+      <c r="E4737" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4738" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4738" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4738" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4738">
+        <v>1794</v>
+      </c>
+      <c r="D4738">
+        <v>3000</v>
+      </c>
+      <c r="E4738" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4739" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4739" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4739" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4739">
+        <v>1590</v>
+      </c>
+      <c r="D4739">
+        <v>8000</v>
+      </c>
+      <c r="E4739" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4740" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4740" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4740" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4740">
+        <v>940</v>
+      </c>
+      <c r="D4740">
+        <v>1000</v>
+      </c>
+      <c r="E4740" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4741" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4741" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4741" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4741">
+        <v>696</v>
+      </c>
+      <c r="D4741">
+        <v>750</v>
+      </c>
+      <c r="E4741" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4742" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4742" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B4742" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4742">
+        <v>208</v>
+      </c>
+      <c r="D4742">
+        <v>7200</v>
+      </c>
+      <c r="E4742" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4743" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4743" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4743" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4743">
+        <v>11952</v>
+      </c>
+      <c r="D4743">
+        <v>12750</v>
+      </c>
+      <c r="E4743" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4744" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4744" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4744" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4744">
+        <v>11259</v>
+      </c>
+      <c r="D4744">
+        <v>12000</v>
+      </c>
+      <c r="E4744" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4745" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4745" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4745" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4745">
+        <v>10123</v>
+      </c>
+      <c r="D4745">
+        <v>11500</v>
+      </c>
+      <c r="E4745" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4746" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4746" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4746" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4746">
+        <v>8724</v>
+      </c>
+      <c r="D4746">
+        <v>8000</v>
+      </c>
+      <c r="E4746" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4747" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4747" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4747" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4747">
+        <v>8324</v>
+      </c>
+      <c r="D4747">
+        <v>8000</v>
+      </c>
+      <c r="E4747" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4748" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4748" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4748" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4748">
+        <v>6522</v>
+      </c>
+      <c r="D4748">
+        <v>3750</v>
+      </c>
+      <c r="E4748" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4749" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4749" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4749" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4749">
+        <v>6394</v>
+      </c>
+      <c r="D4749">
+        <v>6000</v>
+      </c>
+      <c r="E4749" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4750" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4750" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4750" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4750">
+        <v>5772</v>
+      </c>
+      <c r="D4750">
+        <v>3250</v>
+      </c>
+      <c r="E4750" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4751" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4751" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4751" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4751">
+        <v>4476</v>
+      </c>
+      <c r="D4751">
+        <v>3000</v>
+      </c>
+      <c r="E4751" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4752" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4752" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4752" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4752">
+        <v>3931</v>
+      </c>
+      <c r="D4752">
+        <v>20000</v>
+      </c>
+      <c r="E4752" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4753" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4753" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4753" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4753">
+        <v>3809</v>
+      </c>
+      <c r="D4753">
+        <v>12000</v>
+      </c>
+      <c r="E4753" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4754" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4754" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4754" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4754">
+        <v>3698</v>
+      </c>
+      <c r="D4754">
+        <v>8000</v>
+      </c>
+      <c r="E4754" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4755" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4755" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4755" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4755">
+        <v>3567</v>
+      </c>
+      <c r="D4755">
+        <v>8000</v>
+      </c>
+      <c r="E4755" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4756" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4756" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4756" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4756">
+        <v>3567</v>
+      </c>
+      <c r="D4756">
+        <v>8000</v>
+      </c>
+      <c r="E4756" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4757" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4757" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4757" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4757">
+        <v>3544</v>
+      </c>
+      <c r="D4757">
+        <v>8000</v>
+      </c>
+      <c r="E4757" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4758" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4758" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4758" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4758">
+        <v>3422</v>
+      </c>
+      <c r="D4758">
+        <v>8000</v>
+      </c>
+      <c r="E4758" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4759" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4759" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4759" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4759">
+        <v>3422</v>
+      </c>
+      <c r="D4759">
+        <v>8000</v>
+      </c>
+      <c r="E4759" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4760" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4760" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4760" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4760">
+        <v>3341</v>
+      </c>
+      <c r="D4760">
+        <v>8000</v>
+      </c>
+      <c r="E4760" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4761" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4761" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4761" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4761">
+        <v>3290</v>
+      </c>
+      <c r="D4761">
+        <v>8000</v>
+      </c>
+      <c r="E4761" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4762" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4762" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4762" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4762">
+        <v>3204</v>
+      </c>
+      <c r="D4762">
+        <v>8000</v>
+      </c>
+      <c r="E4762" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4763" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4763" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4763" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4763">
+        <v>3194</v>
+      </c>
+      <c r="D4763">
+        <v>8000</v>
+      </c>
+      <c r="E4763" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4764" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4764" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4764" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4764">
+        <v>3162</v>
+      </c>
+      <c r="D4764">
+        <v>2750</v>
+      </c>
+      <c r="E4764" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4765" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4765" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4765" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4765">
+        <v>2844</v>
+      </c>
+      <c r="D4765">
+        <v>3000</v>
+      </c>
+      <c r="E4765" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4766" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4766" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4766" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4766">
+        <v>2685</v>
+      </c>
+      <c r="D4766">
+        <v>6400</v>
+      </c>
+      <c r="E4766" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4767" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4767" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4767" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4767">
+        <v>2369</v>
+      </c>
+      <c r="D4767">
+        <v>2250</v>
+      </c>
+      <c r="E4767" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4768" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4768" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4768" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4768">
+        <v>1888</v>
+      </c>
+      <c r="D4768">
+        <v>1750</v>
+      </c>
+      <c r="E4768" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4769" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4769" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4769" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4769">
+        <v>1443</v>
+      </c>
+      <c r="D4769">
+        <v>8000</v>
+      </c>
+      <c r="E4769" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4770" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4770" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4770" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4770">
+        <v>1274</v>
+      </c>
+      <c r="D4770">
+        <v>1000</v>
+      </c>
+      <c r="E4770" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4771" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4771" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B4771" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4771">
+        <v>248</v>
+      </c>
+      <c r="D4771">
+        <v>14400</v>
+      </c>
+      <c r="E4771" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4772" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4772" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4772" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4772">
+        <v>14424</v>
+      </c>
+      <c r="D4772">
+        <v>15000</v>
+      </c>
+      <c r="E4772" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4773" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4773" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4773" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4773">
+        <v>11998</v>
+      </c>
+      <c r="D4773">
+        <v>13000</v>
+      </c>
+      <c r="E4773" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4774" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4774" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4774" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4774">
+        <v>11808</v>
+      </c>
+      <c r="D4774">
+        <v>13000</v>
+      </c>
+      <c r="E4774" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4775" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4775" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4775" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4775">
+        <v>7952</v>
+      </c>
+      <c r="D4775">
+        <v>7500</v>
+      </c>
+      <c r="E4775" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4776" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4776" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4776" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4776">
+        <v>7372</v>
+      </c>
+      <c r="D4776">
+        <v>7500</v>
+      </c>
+      <c r="E4776" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4777" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4777" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4777" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4777">
+        <v>5818</v>
+      </c>
+      <c r="D4777">
+        <v>4000</v>
+      </c>
+      <c r="E4777" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4778" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4778" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4778" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4778">
+        <v>5750</v>
+      </c>
+      <c r="D4778">
+        <v>4000</v>
+      </c>
+      <c r="E4778" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4779" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4779" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4779" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4779">
+        <v>5512</v>
+      </c>
+      <c r="D4779">
+        <v>5000</v>
+      </c>
+      <c r="E4779" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4780" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4780" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4780" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4780">
+        <v>5086</v>
+      </c>
+      <c r="D4780">
+        <v>4000</v>
+      </c>
+      <c r="E4780" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4781" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4781" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4781" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4781">
+        <v>5086</v>
+      </c>
+      <c r="D4781">
+        <v>4500</v>
+      </c>
+      <c r="E4781" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4782" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4782" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4782" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4782">
+        <v>5064</v>
+      </c>
+      <c r="D4782">
+        <v>5000</v>
+      </c>
+      <c r="E4782" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4783" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4783" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4783" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4783">
+        <v>3837</v>
+      </c>
+      <c r="D4783">
+        <v>4000</v>
+      </c>
+      <c r="E4783" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4784" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4784" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4784" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4784">
+        <v>3837</v>
+      </c>
+      <c r="D4784">
+        <v>4000</v>
+      </c>
+      <c r="E4784" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4785" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4785" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4785" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4785">
+        <v>3800</v>
+      </c>
+      <c r="D4785">
+        <v>4375</v>
+      </c>
+      <c r="E4785" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4786" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4786" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4786" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4786">
+        <v>3516</v>
+      </c>
+      <c r="D4786">
+        <v>4000</v>
+      </c>
+      <c r="E4786" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4787" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4787" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4787" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4787">
+        <v>3448</v>
+      </c>
+      <c r="D4787">
+        <v>7000</v>
+      </c>
+      <c r="E4787" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4788" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4788" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4788" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4788">
+        <v>3448</v>
+      </c>
+      <c r="D4788">
+        <v>7000</v>
+      </c>
+      <c r="E4788" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4789" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4789" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4789" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4789">
+        <v>3420</v>
+      </c>
+      <c r="D4789">
+        <v>4000</v>
+      </c>
+      <c r="E4789" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4790" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4790" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4790" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4790">
+        <v>3292</v>
+      </c>
+      <c r="D4790">
+        <v>14000</v>
+      </c>
+      <c r="E4790" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4791" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4791" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4791" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4791">
+        <v>3246</v>
+      </c>
+      <c r="D4791">
+        <v>3750</v>
+      </c>
+      <c r="E4791" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4792" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4792" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4792" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4792">
+        <v>3246</v>
+      </c>
+      <c r="D4792">
+        <v>3750</v>
+      </c>
+      <c r="E4792" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4793" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4793" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4793" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4793">
+        <v>3226</v>
+      </c>
+      <c r="D4793">
+        <v>3500</v>
+      </c>
+      <c r="E4793" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4794" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4794" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4794" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4794">
+        <v>3217</v>
+      </c>
+      <c r="D4794">
+        <v>7000</v>
+      </c>
+      <c r="E4794" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4795" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4795" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4795" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4795">
+        <v>3205</v>
+      </c>
+      <c r="D4795">
+        <v>7000</v>
+      </c>
+      <c r="E4795" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4796" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4796" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4796" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4796">
+        <v>3156</v>
+      </c>
+      <c r="D4796">
+        <v>7000</v>
+      </c>
+      <c r="E4796" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4797" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4797" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4797" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4797">
+        <v>3083</v>
+      </c>
+      <c r="D4797">
+        <v>7000</v>
+      </c>
+      <c r="E4797" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4798" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4798" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4798" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4798">
+        <v>3010</v>
+      </c>
+      <c r="D4798">
+        <v>7000</v>
+      </c>
+      <c r="E4798" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4799" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4799" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4799" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4799">
+        <v>2983</v>
+      </c>
+      <c r="D4799">
+        <v>7000</v>
+      </c>
+      <c r="E4799" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4800" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4800" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4800" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4800">
+        <v>2959</v>
+      </c>
+      <c r="D4800">
+        <v>7000</v>
+      </c>
+      <c r="E4800" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4801" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4801" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4801" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4801">
+        <v>2633</v>
+      </c>
+      <c r="D4801">
+        <v>3500</v>
+      </c>
+      <c r="E4801" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4802" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4802" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4802" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4802">
+        <v>2410</v>
+      </c>
+      <c r="D4802">
+        <v>4000</v>
+      </c>
+      <c r="E4802" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4803" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4803" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4803" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4803">
+        <v>2250</v>
+      </c>
+      <c r="D4803">
+        <v>5600</v>
+      </c>
+      <c r="E4803" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4804" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4804" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4804" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4804">
+        <v>1932</v>
+      </c>
+      <c r="D4804">
+        <v>7000</v>
+      </c>
+      <c r="E4804" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4805" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4805" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4805" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4805">
+        <v>660</v>
+      </c>
+      <c r="D4805">
+        <v>500</v>
+      </c>
+      <c r="E4805" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4806" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4806" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B4806" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4806">
+        <v>178</v>
+      </c>
+      <c r="D4806">
+        <v>6300</v>
+      </c>
+      <c r="E4806" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4807" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4807" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4807" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4807">
+        <v>13254</v>
+      </c>
+      <c r="D4807">
+        <v>18500</v>
+      </c>
+      <c r="E4807" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4808" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4808" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4808" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4808">
+        <v>12618</v>
+      </c>
+      <c r="D4808">
+        <v>18000</v>
+      </c>
+      <c r="E4808" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4809" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4809" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4809" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4809">
+        <v>7114</v>
+      </c>
+      <c r="D4809">
+        <v>12500</v>
+      </c>
+      <c r="E4809" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4810" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4810" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4810" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4810">
+        <v>6612</v>
+      </c>
+      <c r="D4810">
+        <v>6500</v>
+      </c>
+      <c r="E4810" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4811" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4811" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4811" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4811">
+        <v>5547</v>
+      </c>
+      <c r="D4811">
+        <v>12000</v>
+      </c>
+      <c r="E4811" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4812" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4812" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4812" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4812">
+        <v>5540</v>
+      </c>
+      <c r="D4812">
+        <v>6000</v>
+      </c>
+      <c r="E4812" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4813" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4813" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4813" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4813">
+        <v>5128</v>
+      </c>
+      <c r="D4813">
+        <v>5500</v>
+      </c>
+      <c r="E4813" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4814" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4814" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4814" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4814">
+        <v>4720</v>
+      </c>
+      <c r="D4814">
+        <v>4500</v>
+      </c>
+      <c r="E4814" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4815" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4815" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4815" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4815">
+        <v>4364</v>
+      </c>
+      <c r="D4815">
+        <v>1800</v>
+      </c>
+      <c r="E4815" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4816" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4816" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4816" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4816">
+        <v>3641</v>
+      </c>
+      <c r="D4816">
+        <v>2750</v>
+      </c>
+      <c r="E4816" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4817" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4817" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4817" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4817">
+        <v>3561</v>
+      </c>
+      <c r="D4817">
+        <v>2750</v>
+      </c>
+      <c r="E4817" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4818" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4818" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4818" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4818">
+        <v>3414</v>
+      </c>
+      <c r="D4818">
+        <v>2750</v>
+      </c>
+      <c r="E4818" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4819" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4819" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4819" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4819">
+        <v>3259</v>
+      </c>
+      <c r="D4819">
+        <v>2750</v>
+      </c>
+      <c r="E4819" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4820" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4820" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4820" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4820">
+        <v>3195</v>
+      </c>
+      <c r="D4820">
+        <v>2750</v>
+      </c>
+      <c r="E4820" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4821" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4821" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4821" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4821">
+        <v>3195</v>
+      </c>
+      <c r="D4821">
+        <v>2750</v>
+      </c>
+      <c r="E4821" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4822" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4822" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4822" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4822">
+        <v>3088</v>
+      </c>
+      <c r="D4822">
+        <v>2750</v>
+      </c>
+      <c r="E4822" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4823" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4823" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4823" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4823">
+        <v>3084</v>
+      </c>
+      <c r="D4823">
+        <v>2750</v>
+      </c>
+      <c r="E4823" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4824" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4824" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4824" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4824">
+        <v>3059</v>
+      </c>
+      <c r="D4824">
+        <v>2750</v>
+      </c>
+      <c r="E4824" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4825" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4825" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4825" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4825">
+        <v>1312</v>
+      </c>
+      <c r="D4825">
+        <v>600</v>
+      </c>
+      <c r="E4825" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4826" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4826" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B4826" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4826">
+        <v>193</v>
+      </c>
+      <c r="D4826">
+        <v>450</v>
+      </c>
+      <c r="E4826" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4827" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4827" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4827" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4827">
+        <v>14543</v>
+      </c>
+      <c r="D4827">
+        <v>15000</v>
+      </c>
+      <c r="E4827" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4828" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4828" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4828" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4828">
+        <v>12550</v>
+      </c>
+      <c r="D4828">
+        <v>20000</v>
+      </c>
+      <c r="E4828" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4829" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4829" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4829" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4829">
+        <v>11651</v>
+      </c>
+      <c r="D4829">
+        <v>12500</v>
+      </c>
+      <c r="E4829" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4830" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4830" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4830" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4830">
+        <v>6908</v>
+      </c>
+      <c r="D4830">
+        <v>4000</v>
+      </c>
+      <c r="E4830" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4831" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4831" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4831" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4831">
+        <v>6518</v>
+      </c>
+      <c r="D4831">
+        <v>4000</v>
+      </c>
+      <c r="E4831" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4832" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4832" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4832" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4832">
+        <v>5559</v>
+      </c>
+      <c r="D4832">
+        <v>5500</v>
+      </c>
+      <c r="E4832" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4833" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4833" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4833" t="s">
+        <v>417</v>
+      </c>
+      <c r="C4833">
+        <v>5351</v>
+      </c>
+      <c r="D4833">
+        <v>4000</v>
+      </c>
+      <c r="E4833" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4834" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4834" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4834" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4834">
+        <v>4791</v>
+      </c>
+      <c r="D4834">
+        <v>4000</v>
+      </c>
+      <c r="E4834" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4835" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4835" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4835" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4835">
+        <v>4527</v>
+      </c>
+      <c r="D4835">
+        <v>5000</v>
+      </c>
+      <c r="E4835" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4836" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4836" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4836" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4836">
+        <v>4179</v>
+      </c>
+      <c r="D4836">
+        <v>12000</v>
+      </c>
+      <c r="E4836" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4837" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4837" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4837" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4837">
+        <v>3978</v>
+      </c>
+      <c r="D4837">
+        <v>4375</v>
+      </c>
+      <c r="E4837" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4838" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4838" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4838" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4838">
+        <v>3862</v>
+      </c>
+      <c r="D4838">
+        <v>8000</v>
+      </c>
+      <c r="E4838" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4839" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4839" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4839" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4839">
+        <v>3756</v>
+      </c>
+      <c r="D4839">
+        <v>8000</v>
+      </c>
+      <c r="E4839" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4840" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4840" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4840" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4840">
+        <v>3630</v>
+      </c>
+      <c r="D4840">
+        <v>8000</v>
+      </c>
+      <c r="E4840" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4841" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4841" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4841" t="s">
+        <v>418</v>
+      </c>
+      <c r="C4841">
+        <v>3551</v>
+      </c>
+      <c r="D4841">
+        <v>3750</v>
+      </c>
+      <c r="E4841" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4842" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4842" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4842" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4842">
+        <v>3551</v>
+      </c>
+      <c r="D4842">
+        <v>3750</v>
+      </c>
+      <c r="E4842" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4843" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4843" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4843" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4843">
+        <v>3495</v>
+      </c>
+      <c r="D4843">
+        <v>8000</v>
+      </c>
+      <c r="E4843" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4844" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4844" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4844" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4844">
+        <v>3450</v>
+      </c>
+      <c r="D4844">
+        <v>8000</v>
+      </c>
+      <c r="E4844" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4845" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4845" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4845" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4845">
+        <v>3381</v>
+      </c>
+      <c r="D4845">
+        <v>3750</v>
+      </c>
+      <c r="E4845" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4846" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4846" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4846" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4846">
+        <v>3381</v>
+      </c>
+      <c r="D4846">
+        <v>3750</v>
+      </c>
+      <c r="E4846" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4847" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4847" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4847" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4847">
+        <v>3298</v>
+      </c>
+      <c r="D4847">
+        <v>8000</v>
+      </c>
+      <c r="E4847" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4848" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4848" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4848" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4848">
+        <v>3274</v>
+      </c>
+      <c r="D4848">
+        <v>8000</v>
+      </c>
+      <c r="E4848" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4849" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4849" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4849" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4849">
+        <v>3211</v>
+      </c>
+      <c r="D4849">
+        <v>20000</v>
+      </c>
+      <c r="E4849" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4850" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4850" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4850" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4850">
+        <v>3168</v>
+      </c>
+      <c r="D4850">
+        <v>3500</v>
+      </c>
+      <c r="E4850" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4851" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4851" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4851" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4851">
+        <v>3093</v>
+      </c>
+      <c r="D4851">
+        <v>8000</v>
+      </c>
+      <c r="E4851" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4852" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4852" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4852" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4852">
+        <v>2890</v>
+      </c>
+      <c r="D4852">
+        <v>4000</v>
+      </c>
+      <c r="E4852" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4853" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4853" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4853" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4853">
+        <v>2828</v>
+      </c>
+      <c r="D4853">
+        <v>3725</v>
+      </c>
+      <c r="E4853" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4854" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4854" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4854" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4854">
+        <v>2828</v>
+      </c>
+      <c r="D4854">
+        <v>3875</v>
+      </c>
+      <c r="E4854" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4855" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4855" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4855" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4855">
+        <v>2703</v>
+      </c>
+      <c r="D4855">
+        <v>4000</v>
+      </c>
+      <c r="E4855" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4856" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4856" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4856" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4856">
+        <v>2688</v>
+      </c>
+      <c r="D4856">
+        <v>3000</v>
+      </c>
+      <c r="E4856" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4857" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4857" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4857" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4857">
+        <v>2616</v>
+      </c>
+      <c r="D4857">
+        <v>8000</v>
+      </c>
+      <c r="E4857" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4858" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4858" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4858" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4858">
+        <v>2427</v>
+      </c>
+      <c r="D4858">
+        <v>10400</v>
+      </c>
+      <c r="E4858" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4859" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4859" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4859" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4859">
+        <v>1220</v>
+      </c>
+      <c r="D4859">
+        <v>1000</v>
+      </c>
+      <c r="E4859" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>AM</v>
+      </c>
+    </row>
+    <row r="4860" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4860" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4860" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4860">
+        <v>675</v>
+      </c>
+      <c r="D4860">
+        <v>500</v>
+      </c>
+      <c r="E4860" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4861" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4861" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4861" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4861">
+        <v>675</v>
+      </c>
+      <c r="D4861">
+        <v>500</v>
+      </c>
+      <c r="E4861" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>PM</v>
+      </c>
+    </row>
+    <row r="4862" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4862" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4862" t="s">
+        <v>421</v>
+      </c>
+      <c r="C4862">
+        <v>660</v>
+      </c>
+      <c r="D4862">
+        <v>500</v>
+      </c>
+      <c r="E4862" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4863" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4863" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4863" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4863">
+        <v>540</v>
+      </c>
+      <c r="D4863">
+        <v>500</v>
+      </c>
+      <c r="E4863" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4864" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4864" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4864" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4864">
+        <v>213</v>
+      </c>
+      <c r="D4864">
+        <v>7200</v>
+      </c>
+      <c r="E4864" s="15" t="str">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>NIGHT</v>
+      </c>
+    </row>
+    <row r="4865" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4865" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B4865" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4865">
+        <v>120</v>
+      </c>
+      <c r="D4865">
+        <v>4000</v>
+      </c>
+      <c r="E4865" s="15" t="e">
+        <f>VLOOKUP(Table2[[#This Row],[Name]],Sheet1!A:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -81772,15 +89960,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="600178de-73d9-456f-9bfc-96547beb5665" xsi:nil="true"/>
@@ -81789,6 +89968,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -82027,26 +90215,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC04B04C-240C-4300-803F-B076B2FBA18D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E073380-EFC4-437F-BF84-AC5EBBF6C828}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="295520e8-909a-4e45-b9af-bc3b6c481701"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="600178de-73d9-456f-9bfc-96547beb5665"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E073380-EFC4-437F-BF84-AC5EBBF6C828}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC04B04C-240C-4300-803F-B076B2FBA18D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="600178de-73d9-456f-9bfc-96547beb5665"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="295520e8-909a-4e45-b9af-bc3b6c481701"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
